--- a/data/trans_orig/IP26C-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP26C-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42600</t>
+          <t>43131</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49365</t>
+          <t>49320</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47696</t>
+          <t>47140</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55859</t>
+          <t>55802</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>94293</t>
+          <t>93787</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>104518</t>
+          <t>104025</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,6%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>1878</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8598</t>
+          <t>8067</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2910</t>
+          <t>2967</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11073</t>
+          <t>11629</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5449</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15674</t>
+          <t>16180</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>85769</t>
+          <t>85460</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>95611</t>
+          <t>95273</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>95213</t>
+          <t>95149</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>104214</t>
+          <t>104152</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>184497</t>
+          <t>184273</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>197294</t>
+          <t>197928</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>94,11%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>5708</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15092</t>
+          <t>15298</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4543</t>
+          <t>4605</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13544</t>
+          <t>13608</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11990</t>
+          <t>12192</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>24980</t>
+          <t>25556</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3340</t>
+          <t>4443</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>53733</t>
+          <t>53555</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>62740</t>
+          <t>63163</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>54675</t>
+          <t>55348</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64047</t>
+          <t>64093</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>111851</t>
+          <t>112623</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>124892</t>
+          <t>124876</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,96%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>4434</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13864</t>
+          <t>14042</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4437</t>
+          <t>4380</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13744</t>
+          <t>13058</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11281</t>
+          <t>11345</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23650</t>
+          <t>23462</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,09%</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4810</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4452</t>
+          <t>4444</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>53163</t>
+          <t>52430</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>64482</t>
+          <t>63794</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>62825</t>
+          <t>63221</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72460</t>
+          <t>72495</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>118662</t>
+          <t>119425</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>134403</t>
+          <t>134216</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,51%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9737</t>
+          <t>10510</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20783</t>
+          <t>21637</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5472</t>
+          <t>5663</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14419</t>
+          <t>14724</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17859</t>
+          <t>17910</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32733</t>
+          <t>31992</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>20,86%</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4395</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4973</t>
+          <t>4999</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35839</t>
+          <t>35809</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>40592</t>
+          <t>40593</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40183</t>
+          <t>40110</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>78107</t>
+          <t>78541</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>83991</t>
+          <t>83982</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>637</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5421</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3309</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>667</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6542</t>
+          <t>6108</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>40432</t>
+          <t>40183</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>49964</t>
+          <t>49773</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>43014</t>
+          <t>43370</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>52208</t>
+          <t>52598</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>86596</t>
+          <t>86978</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>99895</t>
+          <t>99491</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,41%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6091</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15623</t>
+          <t>15872</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6870</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16064</t>
+          <t>15708</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>15238</t>
+          <t>15642</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28537</t>
+          <t>28155</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,45%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>106753</t>
+          <t>106059</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>118621</t>
+          <t>118678</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>116730</t>
+          <t>116602</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>127964</t>
+          <t>127992</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>227362</t>
+          <t>227311</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>243905</t>
+          <t>243894</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>9944</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>21869</t>
+          <t>22563</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6574</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17482</t>
+          <t>16897</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>19536</t>
+          <t>19359</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>35669</t>
+          <t>35627</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5061</t>
+          <t>5077</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>140042</t>
+          <t>139636</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>150995</t>
+          <t>150381</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>146483</t>
+          <t>147018</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>156494</t>
+          <t>156703</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>290057</t>
+          <t>290041</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>304604</t>
+          <t>304662</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,03%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>5546</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>14856</t>
+          <t>15303</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3868</t>
+          <t>4012</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>12748</t>
+          <t>12783</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>11411</t>
+          <t>11403</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>24529</t>
+          <t>24567</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>773</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6246</t>
+          <t>6559</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>977</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>6569</t>
+          <t>6528</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2527</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>9696</t>
+          <t>10258</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>586422</t>
+          <t>586184</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>613781</t>
+          <t>613347</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>635695</t>
+          <t>634475</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>660419</t>
+          <t>661154</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1229862</t>
+          <t>1230886</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1268979</t>
+          <t>1268681</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,91%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>61995</t>
+          <t>62459</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>89184</t>
+          <t>88973</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>50902</t>
+          <t>49754</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>74007</t>
+          <t>75421</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>117389</t>
+          <t>116898</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>155285</t>
+          <t>153956</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>1657</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>8998</t>
+          <t>8395</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3068</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>11191</t>
+          <t>10492</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>6087</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>16413</t>
+          <t>15820</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>45455</t>
+          <t>45725</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53340</t>
+          <t>53507</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50551</t>
+          <t>51183</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59750</t>
+          <t>59976</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>99698</t>
+          <t>100152</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>111725</t>
+          <t>111852</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,1%</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t>3078</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11130</t>
+          <t>10860</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2436</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10253</t>
+          <t>10052</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7218</t>
+          <t>6647</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18256</t>
+          <t>17631</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,67%</t>
         </is>
       </c>
     </row>
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>596</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5312</t>
+          <t>5087</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>588</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5529,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>92633</t>
+          <t>92108</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>100928</t>
+          <t>100787</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>97732</t>
+          <t>97581</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>106408</t>
+          <t>106019</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>193741</t>
+          <t>193824</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>204976</t>
+          <t>205464</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10020</t>
+          <t>10405</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>2146</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9747</t>
+          <t>9636</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5752</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15960</t>
+          <t>16080</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2559</t>
+          <t>3176</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5498</t>
+          <t>4666</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>627</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>6069</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>52280</t>
+          <t>52123</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>62324</t>
+          <t>61820</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>52485</t>
+          <t>52155</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63224</t>
+          <t>62895</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>109351</t>
+          <t>108828</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>122889</t>
+          <t>123055</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,69%</t>
         </is>
       </c>
     </row>
@@ -6098,12 +6098,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>5680</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15220</t>
+          <t>15377</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7878</t>
+          <t>7862</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18142</t>
+          <t>18154</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15471</t>
+          <t>15114</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28528</t>
+          <t>29180</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -6251,7 +6251,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3248</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3283</t>
+          <t>2925</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69661</t>
+          <t>69442</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>75693</t>
+          <t>75560</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>74838</t>
+          <t>75209</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>80235</t>
+          <t>80212</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>147656</t>
+          <t>147224</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>154760</t>
+          <t>154922</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6687</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4717</t>
+          <t>4613</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1454</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8511</t>
+          <t>8286</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3611</t>
+          <t>3907</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -6897,12 +6897,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>36987</t>
+          <t>36815</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43207</t>
+          <t>43203</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40913</t>
+          <t>40065</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>46100</t>
+          <t>46095</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>80488</t>
+          <t>80666</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>88453</t>
+          <t>88573</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,71%</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7015,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5203</t>
+          <t>5341</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>657</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5839</t>
+          <t>6687</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1534</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>8608</t>
+          <t>9175</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -7353,12 +7353,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>39144</t>
+          <t>38609</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>48847</t>
+          <t>48715</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>40153</t>
+          <t>39985</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>51062</t>
+          <t>51333</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>83259</t>
+          <t>82854</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>97448</t>
+          <t>97639</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>84,0%</t>
         </is>
       </c>
     </row>
@@ -7466,12 +7466,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6527</t>
+          <t>6460</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16036</t>
+          <t>16316</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8288</t>
+          <t>8567</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19033</t>
+          <t>19317</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17525</t>
+          <t>17415</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>31735</t>
+          <t>31859</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,41%</t>
         </is>
       </c>
     </row>
@@ -7584,7 +7584,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7619,7 +7619,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4079</t>
+          <t>3505</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>4404</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -7809,12 +7809,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>106445</t>
+          <t>105384</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>120962</t>
+          <t>120287</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7824,12 +7824,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>113024</t>
+          <t>114044</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>127671</t>
+          <t>127843</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>225024</t>
+          <t>226159</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>245213</t>
+          <t>245434</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,15%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>15728</t>
+          <t>16537</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>30137</t>
+          <t>31106</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>16135</t>
+          <t>15963</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>30782</t>
+          <t>29762</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>35663</t>
+          <t>35526</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>55884</t>
+          <t>54707</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,43%</t>
         </is>
       </c>
     </row>
@@ -8040,7 +8040,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4379</t>
+          <t>4846</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8055,7 +8055,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5816</t>
+          <t>4859</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8125,7 +8125,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -8265,12 +8265,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>143999</t>
+          <t>144753</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>154935</t>
+          <t>155472</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>148446</t>
+          <t>148967</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>159991</t>
+          <t>160398</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>297000</t>
+          <t>296081</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>313090</t>
+          <t>312961</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,48%</t>
         </is>
       </c>
     </row>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>6448</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>16905</t>
+          <t>16234</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>7211</t>
+          <t>7282</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>18002</t>
+          <t>17787</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>15502</t>
+          <t>15599</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>30648</t>
+          <t>31017</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -8496,7 +8496,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>4192</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>723</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5929</t>
+          <t>5962</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>744</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>7387</t>
+          <t>7373</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>616043</t>
+          <t>615872</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>641650</t>
+          <t>641884</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>648913</t>
+          <t>648420</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>676986</t>
+          <t>676917</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1274500</t>
+          <t>1274265</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1314192</t>
+          <t>1312906</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,64%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>57540</t>
+          <t>57658</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>82091</t>
+          <t>83816</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>60985</t>
+          <t>60601</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>88626</t>
+          <t>87046</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>123829</t>
+          <t>124798</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>160296</t>
+          <t>161856</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>9723</t>
+          <t>9551</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>13542</t>
+          <t>13141</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>7019</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>18842</t>
+          <t>19341</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -9413,12 +9413,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44046</t>
+          <t>43985</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53131</t>
+          <t>52651</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>57254</t>
+          <t>57536</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63738</t>
+          <t>63772</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>105465</t>
+          <t>104155</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>115420</t>
+          <t>115237</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,59%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>4413</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12807</t>
+          <t>13169</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>690</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7208</t>
+          <t>6926</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6065</t>
+          <t>6137</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15820</t>
+          <t>16885</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2541</t>
+          <t>2851</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9714,7 +9714,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -9869,12 +9869,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>84191</t>
+          <t>84264</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>95130</t>
+          <t>94810</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>89089</t>
+          <t>88861</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>101055</t>
+          <t>100714</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>177598</t>
+          <t>177180</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>193024</t>
+          <t>192777</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,03%</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9982,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5760</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15155</t>
+          <t>15764</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8579</t>
+          <t>8920</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20545</t>
+          <t>20773</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>17257</t>
+          <t>16851</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>32251</t>
+          <t>31859</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>640</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5324</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10115,7 +10115,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>648</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>5914</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10185,7 +10185,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -10325,12 +10325,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>56529</t>
+          <t>56919</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>63445</t>
+          <t>63894</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10340,12 +10340,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59765</t>
+          <t>59093</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67097</t>
+          <t>67099</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>118849</t>
+          <t>118431</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>128888</t>
+          <t>129344</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,56%</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8302</t>
+          <t>8032</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10473,12 +10473,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10140</t>
+          <t>10812</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5679</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15736</t>
+          <t>16083</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t>3798</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10641,7 +10641,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>63977</t>
+          <t>63331</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>72265</t>
+          <t>71897</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10796,12 +10796,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>64214</t>
+          <t>64201</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74110</t>
+          <t>74244</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10831,12 +10831,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>131537</t>
+          <t>130644</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>144627</t>
+          <t>144218</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,42%</t>
         </is>
       </c>
     </row>
@@ -10894,12 +10894,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>3051</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10384</t>
+          <t>10902</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>6199</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16229</t>
+          <t>16242</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11185</t>
+          <t>11052</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23672</t>
+          <t>24001</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,38%</t>
         </is>
       </c>
     </row>
@@ -11012,7 +11012,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4583</t>
+          <t>3717</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11027,7 +11027,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -11272,7 +11272,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42845</t>
+          <t>42786</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -11287,7 +11287,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>85818</t>
+          <t>85650</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -11322,7 +11322,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2843</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11425,7 +11425,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3308</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11440,7 +11440,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -11693,7 +11693,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>50090</t>
+          <t>49870</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -11708,7 +11708,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -11728,7 +11728,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>52944</t>
+          <t>53904</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>106212</t>
+          <t>106209</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>111379</t>
+          <t>111376</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -11811,7 +11811,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4183</t>
+          <t>4403</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11826,7 +11826,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11846,7 +11846,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>3835</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11861,7 +11861,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>636</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>5803</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>117249</t>
+          <t>117026</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>128673</t>
+          <t>128338</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>118691</t>
+          <t>119155</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>131317</t>
+          <t>131192</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>240104</t>
+          <t>240116</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>256746</t>
+          <t>256339</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,35%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6790</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>18171</t>
+          <t>18131</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8439</t>
+          <t>8214</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>20225</t>
+          <t>19739</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>18356</t>
+          <t>18350</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>34549</t>
+          <t>33504</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12352,7 +12352,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -12380,7 +12380,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>2861</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12395,7 +12395,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>711</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6926</t>
+          <t>6790</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12430,7 +12430,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7162</t>
+          <t>7738</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>135021</t>
+          <t>134280</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>148313</t>
+          <t>148553</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>143145</t>
+          <t>143584</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>156656</t>
+          <t>156872</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>282489</t>
+          <t>282628</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>301491</t>
+          <t>301974</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>91,02%</t>
         </is>
       </c>
     </row>
@@ -12718,12 +12718,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>12549</t>
+          <t>12606</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>25237</t>
+          <t>26414</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12733,12 +12733,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>11958</t>
+          <t>11924</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>24832</t>
+          <t>25118</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>27844</t>
+          <t>27809</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>47077</t>
+          <t>46224</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -12831,12 +12831,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>476</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12846,12 +12846,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>3722</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12886,7 +12886,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>686</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6280</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12921,7 +12921,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>618748</t>
+          <t>618171</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>643814</t>
+          <t>643296</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>654697</t>
+          <t>655990</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>682042</t>
+          <t>683063</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1282914</t>
+          <t>1283267</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1318549</t>
+          <t>1318282</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,84%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>47347</t>
+          <t>48049</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>70655</t>
+          <t>73036</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>53618</t>
+          <t>52859</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>79651</t>
+          <t>78598</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>108232</t>
+          <t>108170</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>142180</t>
+          <t>142307</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13264,7 +13264,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3186</t>
+          <t>3007</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>11768</t>
+          <t>11709</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>8417</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>5535</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>16063</t>
+          <t>15697</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -13753,7 +13753,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>69978</t>
+          <t>70194</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -13788,12 +13788,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>71932</t>
+          <t>72566</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>78789</t>
+          <t>78763</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13803,12 +13803,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13823,12 +13823,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>144744</t>
+          <t>144813</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>151886</t>
+          <t>151933</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13838,12 +13838,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -13871,7 +13871,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>3088</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13886,7 +13886,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>603</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7434</t>
+          <t>6800</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13916,12 +13916,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13936,12 +13936,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>715</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7904</t>
+          <t>7835</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -14209,12 +14209,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>116308</t>
+          <t>115700</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>124129</t>
+          <t>124292</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14224,12 +14224,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>115388</t>
+          <t>115164</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>126477</t>
+          <t>126498</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -14259,12 +14259,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14279,12 +14279,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>235529</t>
+          <t>235752</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>248947</t>
+          <t>248683</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14294,12 +14294,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>801</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8207</t>
+          <t>8421</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -14337,12 +14337,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12208</t>
+          <t>12432</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14372,12 +14372,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14392,12 +14392,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3386</t>
+          <t>3944</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>16448</t>
+          <t>16601</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -14440,7 +14440,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4667</t>
+          <t>4453</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14455,7 +14455,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14510,7 +14510,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4190</t>
+          <t>4034</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14525,7 +14525,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -14665,12 +14665,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>47616</t>
+          <t>47623</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>55465</t>
+          <t>55322</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>57066</t>
+          <t>56395</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64921</t>
+          <t>65170</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>108326</t>
+          <t>107386</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>118823</t>
+          <t>118928</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,82%</t>
         </is>
       </c>
     </row>
@@ -14778,12 +14778,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>2946</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10652</t>
+          <t>10645</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14793,12 +14793,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14813,12 +14813,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2242</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10097</t>
+          <t>10768</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14828,12 +14828,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6608</t>
+          <t>6503</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17105</t>
+          <t>18045</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14863,12 +14863,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -15121,12 +15121,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>59582</t>
+          <t>59372</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>67420</t>
+          <t>67310</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>65192</t>
+          <t>66158</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>76742</t>
+          <t>77190</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>129488</t>
+          <t>129572</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>142583</t>
+          <t>142878</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15206,12 +15206,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,36%</t>
         </is>
       </c>
     </row>
@@ -15234,12 +15234,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2693</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10146</t>
+          <t>10526</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>944</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12942</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15284,12 +15284,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5091</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18384</t>
+          <t>18321</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15319,12 +15319,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -15352,7 +15352,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15367,7 +15367,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15422,7 +15422,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15577,7 +15577,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>30507</t>
+          <t>30865</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -15592,7 +15592,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -15612,12 +15612,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>33148</t>
+          <t>33005</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38954</t>
+          <t>38908</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15647,12 +15647,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>66347</t>
+          <t>66174</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>72800</t>
+          <t>72974</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15662,12 +15662,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>97,0%</t>
         </is>
       </c>
     </row>
@@ -15695,7 +15695,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>3648</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15710,7 +15710,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1811</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7714</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15760,12 +15760,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>2258</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>8885</t>
+          <t>9058</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15775,12 +15775,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,04%</t>
         </is>
       </c>
     </row>
@@ -16033,12 +16033,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>24629</t>
+          <t>24266</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>34588</t>
+          <t>34439</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>32299</t>
+          <t>31811</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>43106</t>
+          <t>43197</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>58575</t>
+          <t>59430</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>74645</t>
+          <t>74633</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -16118,12 +16118,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>72,92%</t>
         </is>
       </c>
     </row>
@@ -16146,12 +16146,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8685</t>
+          <t>9281</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18749</t>
+          <t>18881</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9643</t>
+          <t>9515</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20394</t>
+          <t>19891</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -16196,12 +16196,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21572</t>
+          <t>21772</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>36370</t>
+          <t>35984</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16231,12 +16231,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,16%</t>
         </is>
       </c>
     </row>
@@ -16259,12 +16259,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>952</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>5960</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -16274,12 +16274,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1792</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7363</t>
+          <t>7341</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16329,12 +16329,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3636</t>
+          <t>3586</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10939</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16344,12 +16344,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -16489,12 +16489,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>109748</t>
+          <t>109690</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>119726</t>
+          <t>119590</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16524,12 +16524,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>132329</t>
+          <t>133916</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>146461</t>
+          <t>147281</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16539,12 +16539,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16559,12 +16559,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>247630</t>
+          <t>247319</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>263071</t>
+          <t>263189</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16574,12 +16574,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,96%</t>
         </is>
       </c>
     </row>
@@ -16602,12 +16602,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4782</t>
+          <t>4918</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14760</t>
+          <t>14818</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16617,12 +16617,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16637,12 +16637,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8302</t>
+          <t>7876</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>21459</t>
+          <t>20449</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16652,12 +16652,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16672,12 +16672,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>16155</t>
+          <t>15889</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>31722</t>
+          <t>31836</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16687,12 +16687,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -16755,7 +16755,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4567</t>
+          <t>5585</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16770,7 +16770,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16790,7 +16790,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4450</t>
+          <t>4853</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16805,7 +16805,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -16945,12 +16945,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>107640</t>
+          <t>108472</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>120926</t>
+          <t>120979</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16980,12 +16980,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>120675</t>
+          <t>119207</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>136601</t>
+          <t>136279</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16995,12 +16995,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17015,12 +17015,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>231785</t>
+          <t>231632</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>253886</t>
+          <t>254146</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -17030,12 +17030,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,12%</t>
         </is>
       </c>
     </row>
@@ -17058,12 +17058,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>10693</t>
+          <t>10640</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>23979</t>
+          <t>23147</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17093,12 +17093,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>19589</t>
+          <t>19889</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>35576</t>
+          <t>36661</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -17108,12 +17108,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17128,12 +17128,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>34073</t>
+          <t>33635</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>55972</t>
+          <t>56001</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17143,12 +17143,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -17211,7 +17211,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3875</t>
+          <t>4335</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17226,7 +17226,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17246,7 +17246,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4379</t>
+          <t>3637</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17261,7 +17261,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -17401,12 +17401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>590105</t>
+          <t>590672</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>616482</t>
+          <t>616500</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17416,12 +17416,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17436,12 +17436,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>662807</t>
+          <t>662358</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>694049</t>
+          <t>694501</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17451,12 +17451,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1259418</t>
+          <t>1259823</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1301361</t>
+          <t>1302153</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17486,12 +17486,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,33%</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>43905</t>
+          <t>43925</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>69011</t>
+          <t>69172</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17534,7 +17534,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17549,12 +17549,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>61217</t>
+          <t>62606</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>93255</t>
+          <t>94050</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17564,12 +17564,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>114326</t>
+          <t>115061</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>155101</t>
+          <t>156359</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17599,12 +17599,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -17627,12 +17627,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>8553</t>
+          <t>8842</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17662,12 +17662,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2522</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>9965</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17677,12 +17677,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17697,12 +17697,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>5358</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>15591</t>
+          <t>15090</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17712,12 +17712,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
